--- a/models/6506_DCF_Model_20260906.xlsx
+++ b/models/6506_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77441C0B-80F3-447A-B0C7-3D54635451A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE469236-588C-4593-9140-C0832329DC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
     <t>vs Current Price</t>
   </si>
   <si>
-    <t>DCF - Perpetuity Growth</t>
+    <t>DCF - Perpetuity Growth [参考・Target不算入 — 追補6 §X]</t>
   </si>
   <si>
     <t>DCF - Exit Multiple</t>
@@ -92,7 +92,7 @@
     <t>Comps - PER Median [参考・Target不算入]</t>
   </si>
   <si>
-    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外）</t>
+    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外） ■【追補6 §X】PGMとExitの乖離が **4.53倍** で 3.0倍を超えたため、**乖離そのものを裁定トリガーとする追補6 §X により中点平均を禁止**し、どちらの脚を落とすかを判定した。■**観測倍率バンドテスト**: Peer の実測 EV/EBITDA の第1〜第3四分位バンドは **(14.579873209990334, 15.552094158010673, 5)倍**。これに対し **PGM逆算 3.31倍 / 仮定Exit 15.00倍**。**PGM法のみがバンドの外にあるため PGM法を[参考]に降格し、Target = Exit 単独**とした。■バンドテストは市場倍率を無条件のアンカーにするものではない（それではスクリーナーが市場の複写に堕する）。**実際に取引されているレンジの外に出た脚だけを取り除く**という位置づけである。</t>
   </si>
   <si>
     <t>DCF Valuation Range (PGM - Exit)</t>
@@ -1672,7 +1672,7 @@
     <col min="3" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
@@ -1680,19 +1680,19 @@
       <c r="D1" s="44"/>
       <c r="E1" s="44"/>
     </row>
-    <row r="3" spans="2:5" ht="18" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="43" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
     </row>
-    <row r="4" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
@@ -1724,16 +1724,16 @@
         <v>4570</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <f>IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0))</f>
-        <v>1557</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+        <f>IF(ISNUMBER(C17),ROUND(C17,0),"N/A")</f>
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
@@ -1742,23 +1742,23 @@
         <v>SELL</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="7">
         <f>IF(ISNUMBER(C10),(C10-C9)/C9,"N/A")</f>
-        <v>-0.65929978118161925</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+        <v>-0.45120350109409191</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="10" t="s">
         <v>14</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>17</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>-0.86739606126914659</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>18</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>-0.45120350109409191</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>19</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>-0.18687089715536104</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>-0.10809628008752735</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="45" t="s">
         <v>21</v>
       </c>
@@ -1829,7 +1829,7 @@
       <c r="D20" s="44"/>
       <c r="E20" s="44"/>
     </row>
-    <row r="21" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>22</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>606 - 2508</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>23</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>27</v>
       </c>
@@ -1906,12 +1906,12 @@
     <col min="3" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="10" t="s">
         <v>32</v>
       </c>
@@ -1925,12 +1925,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>37</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>542122</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>38</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>350885</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>39</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>191237</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>40</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>0.35275639062793984</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>41</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>143929</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>42</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>47308</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>43</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>35240</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>44</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>8.7264490280785506E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>45</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>6.5003818328715671E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>46</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>8.257669031137364E-3</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>48</v>
       </c>
@@ -2139,12 +2139,12 @@
         <v>-5.6801642841477762E-2</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>50</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>52170</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>51</v>
       </c>
@@ -2170,7 +2170,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>52</v>
       </c>
@@ -2185,12 +2185,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>56</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>61223</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>57</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>110029</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>58</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>48806</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
@@ -2269,12 +2269,12 @@
     <col min="3" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>61</v>
       </c>
@@ -2284,7 +2284,7 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>62</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>4.095E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>63</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>64</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>2.9700000000000001E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>65</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>1.7073</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>66</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>67</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>68</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>1.9599999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>69</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>5.3699999999999998E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>70</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>71</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>72</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>259367959</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>73</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>63628</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>74</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>542122</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>75</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>76</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>77</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>542122</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>78</v>
       </c>
@@ -2422,7 +2422,7 @@
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>79</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>0.15067450000000002</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>80</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>0.94903672772136272</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>81</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>5.096327227863718E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>82</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>0.14399451456771378</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>83</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>85</v>
       </c>
@@ -2480,7 +2480,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="10" t="s">
         <v>86</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>46</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>91</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>0.64700000000000002</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>92</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>0.25719999999999998</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>37</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>613332.09323101793</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>38</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>396825.86432046862</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>39</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>216506.22891054931</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>40</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>0.35299999999999998</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>93</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>157749.01437901781</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>94</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>9.5799999999999969E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>95</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>58757.214531531499</v>
       </c>
     </row>
-    <row r="40" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>96</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>14689.303632882875</v>
       </c>
     </row>
-    <row r="41" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>97</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>44067.910898648624</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>98</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>23919.9516360097</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>99</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>25100</v>
       </c>
     </row>
-    <row r="44" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>100</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>6606.8205569044803</v>
       </c>
     </row>
-    <row r="45" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>101</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>36281.041977753848</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>102</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>0.51036430234757768</v>
       </c>
     </row>
-    <row r="47" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
         <v>103</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>18516.548677419523</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="22" t="s">
         <v>104</v>
       </c>
@@ -2952,7 +2952,7 @@
       <c r="F49" s="23"/>
       <c r="G49" s="23"/>
     </row>
-    <row r="50" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>105</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>81211.508305075607</v>
       </c>
     </row>
-    <row r="51" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>106</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>273472.77995483548</v>
       </c>
     </row>
-    <row r="52" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>107</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>139570.74455270224</v>
       </c>
     </row>
-    <row r="53" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>108</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>220782.25285777784</v>
       </c>
     </row>
-    <row r="54" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>109</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>157154.25285777784</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>110</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="57" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="22" t="s">
         <v>111</v>
       </c>
@@ -3016,7 +3016,7 @@
       <c r="F57" s="23"/>
       <c r="G57" s="23"/>
     </row>
-    <row r="58" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
         <v>105</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>81211.508305075607</v>
       </c>
     </row>
-    <row r="59" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
         <v>112</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>82677.166167541203</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>113</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>1240157.4925131181</v>
       </c>
     </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>107</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>632932.11346757878</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>108</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>714143.62177265435</v>
       </c>
     </row>
-    <row r="63" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>109</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>650515.62177265435</v>
       </c>
     </row>
-    <row r="64" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
         <v>114</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="22" t="s">
         <v>115</v>
       </c>
@@ -3089,7 +3089,7 @@
       <c r="F66" s="23"/>
       <c r="G66" s="23"/>
     </row>
-    <row r="67" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="25" t="s">
         <v>116</v>
       </c>
@@ -3106,12 +3106,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="68" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="4" t="s">
         <v>84</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="70" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="4" t="s">
         <v>121</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="71" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="4" t="s">
         <v>122</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="72" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
         <v>123</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="73" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
         <v>124</v>
       </c>
@@ -3211,12 +3211,12 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="75" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="76" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="s">
         <v>84</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>0.64700000000000002</v>
       </c>
     </row>
-    <row r="77" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="4" t="s">
         <v>121</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>0.63700000000000001</v>
       </c>
     </row>
-    <row r="78" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="s">
         <v>122</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>0.64700000000000002</v>
       </c>
     </row>
-    <row r="79" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="s">
         <v>123</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>0.65500000000000003</v>
       </c>
     </row>
-    <row r="80" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="4" t="s">
         <v>124</v>
       </c>
@@ -3316,12 +3316,12 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="82" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="83" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="4" t="s">
         <v>84</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>0.25719999999999998</v>
       </c>
     </row>
-    <row r="84" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="4" t="s">
         <v>121</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>0.246</v>
       </c>
     </row>
-    <row r="85" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="4" t="s">
         <v>122</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>0.25719999999999998</v>
       </c>
     </row>
-    <row r="86" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="4" t="s">
         <v>123</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="87" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="4" t="s">
         <v>124</v>
       </c>
@@ -3445,17 +3445,17 @@
     <col min="3" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
         <v>127</v>
       </c>
@@ -3467,7 +3467,7 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>128</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>4570</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>72</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>259367959</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>129</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>1185311.5726300001</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>73</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>63628</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>130</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>1248939.5726300001</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>131</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>0.14399451456771378</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>132</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>133</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>134</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>47308</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>135</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>68301</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>136</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>613332.09323101793</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>137</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>220782.25285777784</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>138</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>0.1228534683562519</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>139</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>1028157.3197722222</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>140</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>3964</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>141</v>
       </c>
@@ -3611,12 +3611,12 @@
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>143</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>167351.05175896475</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>144</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>223134.73567861968</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>145</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>3.2669321924806325</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>146</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>4.7166385321429711</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>147</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>0.3638073698429044</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>148</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>1816267.2870705693</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>149</v>
       </c>
@@ -3682,17 +3682,17 @@
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="28" t="s">
         <v>152</v>
       </c>
@@ -3720,12 +3720,12 @@
         <v>0.16399451456771377</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>155</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>0.81876404686516469</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>156</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>1.4927146451264797</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>157</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>2.0505236047797242</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>158</v>
       </c>
@@ -3837,12 +3837,12 @@
         <v>2.7176593151958137</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>155</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>5.5712569687187514</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>156</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>4.8207560223840362</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>157</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>4.2064474719309413</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>158</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>3.4810557799179014</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="22" t="s">
         <v>160</v>
       </c>
@@ -3966,7 +3966,7 @@
       <c r="H47" s="23"/>
       <c r="I47" s="23"/>
     </row>
-    <row r="48" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>155</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>291948.24132329115</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>156</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>330785.33982444083</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>157</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>372819.72573684715</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>158</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>441442.43407085678</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="22" t="s">
         <v>161</v>
       </c>
@@ -4090,7 +4090,7 @@
       <c r="H52" s="23"/>
       <c r="I52" s="23"/>
     </row>
-    <row r="53" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>155</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>4.2744358255851473</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>156</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>4.8430526613730525</v>
       </c>
     </row>
-    <row r="55" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>157</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>5.4584812189696654</v>
       </c>
     </row>
-    <row r="56" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
         <v>158</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>6.4631913745165779</v>
       </c>
     </row>
-    <row r="58" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
         <v>162</v>
       </c>
@@ -4214,12 +4214,12 @@
       <c r="H58" s="9"/>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="60" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>164</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>279079.62615710037</v>
       </c>
     </row>
-    <row r="62" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="28" t="s">
         <v>165</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="63" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="31">
         <v>6.1400000000000003E-2</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>8.3842212349205436</v>
       </c>
     </row>
-    <row r="64" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="31">
         <v>9.2100000000000001E-2</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>5.5894808232803639</v>
       </c>
     </row>
-    <row r="65" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="4" t="s">
         <v>168</v>
       </c>
@@ -4278,7 +4278,7 @@
         <v>4.1902861246971401</v>
       </c>
     </row>
-    <row r="66" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="31">
         <v>0.15359999999999999</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>3.3515051030216241</v>
       </c>
     </row>
-    <row r="67" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="31">
         <v>0.18429999999999999</v>
       </c>
@@ -4304,7 +4304,7 @@
         <v>2.7932240033864431</v>
       </c>
     </row>
-    <row r="69" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="8" t="s">
         <v>169</v>
       </c>
@@ -4316,7 +4316,7 @@
       <c r="H69" s="9"/>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="6" t="s">
         <v>170</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>18.25881659352066</v>
       </c>
     </row>
-    <row r="71" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
         <v>171</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>2.3037979875931986</v>
       </c>
     </row>
-    <row r="72" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
         <v>172</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>5.0553162387056796</v>
       </c>
     </row>
-    <row r="73" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
         <v>173</v>
       </c>
@@ -4352,7 +4352,7 @@
         <v>4.1219185245293763</v>
       </c>
     </row>
-    <row r="74" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="4" t="s">
         <v>174</v>
       </c>
@@ -4361,12 +4361,12 @@
         <v>15.020840678830101</v>
       </c>
     </row>
-    <row r="75" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="77" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="22" t="s">
         <v>176</v>
       </c>
@@ -4378,13 +4378,13 @@
       <c r="H77" s="23"/>
       <c r="I77" s="23"/>
     </row>
-    <row r="78" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="str">
         <f>"At "&amp;TEXT(C6,"#,##0")&amp;" yen the market is paying for a steady-state operating profit of "&amp;TEXT(F49,"#,##0")&amp;" mn JPY - "&amp;TEXT(F54,"0.00")&amp;"x the FY2023 cycle peak of "&amp;TEXT(C15,"#,##0")&amp;" mn - reached in 5 years and sustained for ever, against "&amp;TEXT(C14,"#,##0")&amp;" mn actually earned in FY2026."</f>
         <v>At 4,570 yen the market is paying for a steady-state operating profit of 279,080 mn JPY - 4.09x the FY2023 cycle peak of 68,301 mn - reached in 5 years and sustained for ever, against 47,308 mn actually earned in FY2026.</v>
       </c>
     </row>
-    <row r="79" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="str">
         <f>"Even with no ramp at all (Block A) the price needs "&amp;TEXT(C25,"#,##0")&amp;" mn, or "&amp;TEXT(C26,"0.00")&amp;"x the peak. The base case supports an EV of only "&amp;TEXT(C17,"#,##0")&amp;" mn, leaving "&amp;TEXT(C20,"#,##0")&amp;" yen per share of the current price unexplained by mid-cycle economics."</f>
         <v>Even with no ramp at all (Block A) the price needs 223,135 mn, or 3.27x the peak. The base case supports an EV of only 220,782 mn, leaving 3,964 yen per share of the current price unexplained by mid-cycle economics.</v>
@@ -4409,12 +4409,12 @@
     <col min="3" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>178</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="33" t="s">
         <v>180</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="33" t="s">
         <v>181</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="33" t="s">
         <v>182</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
         <v>183</v>
       </c>
@@ -4535,7 +4535,7 @@
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
     </row>
-    <row r="9" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
         <v>37</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>613332.09323101793</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="33" t="s">
         <v>38</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>396825.86432046862</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>184</v>
       </c>
@@ -4602,7 +4602,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="33" t="s">
         <v>185</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>181479.08512041077</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="33" t="s">
         <v>186</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>225049.18880640276</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="33" t="s">
         <v>187</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>406528.2739268135</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="33" t="s">
         <v>188</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>69580.425524684906</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="33" t="s">
         <v>189</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>69580.425524684906</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="22" t="s">
         <v>190</v>
       </c>
@@ -4755,7 +4755,7 @@
       <c r="G17" s="23"/>
       <c r="H17" s="23"/>
     </row>
-    <row r="18" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="33" t="s">
         <v>191</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>336947.84840212861</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="33" t="s">
         <v>100</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>6606.8205569044803</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="22" t="s">
         <v>192</v>
       </c>
@@ -4823,7 +4823,7 @@
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
     </row>
-    <row r="23" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="25" t="s">
         <v>86</v>
       </c>
@@ -4840,12 +4840,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>84</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>121</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>122</v>
       </c>
@@ -4905,7 +4905,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>123</v>
       </c>
@@ -4925,7 +4925,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
         <v>124</v>
       </c>
@@ -4945,12 +4945,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>84</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>121</v>
       </c>
@@ -4990,7 +4990,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>122</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>123</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>124</v>
       </c>
@@ -5050,12 +5050,12 @@
         <v>235</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>84</v>
       </c>
@@ -5075,7 +5075,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>121</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>122</v>
       </c>
@@ -5115,7 +5115,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>123</v>
       </c>
@@ -5135,7 +5135,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>124</v>
       </c>
@@ -5176,17 +5176,17 @@
     <col min="17" max="17" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="28" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="28" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>3</v>
       </c>
@@ -5236,7 +5236,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>212</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>483542</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>214</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>1864871</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>216</v>
       </c>
@@ -5397,7 +5397,7 @@
         <v>2115090</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>218</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>835885</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>220</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>4484266</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>222</v>
       </c>
@@ -5556,12 +5556,12 @@
         <v>6568369</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="15" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>225</v>
       </c>
@@ -5590,7 +5590,7 @@
         <v>7.9100180134178688E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>226</v>
       </c>
@@ -5619,7 +5619,7 @@
         <v>8.9305372864932744E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>227</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>9.0930823461409294E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="22" t="s">
         <v>228</v>
       </c>
@@ -5660,12 +5660,12 @@
       <c r="H19" s="23"/>
       <c r="I19" s="23"/>
     </row>
-    <row r="20" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>230</v>
       </c>
@@ -5673,7 +5673,7 @@
         <v>68402</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>231</v>
       </c>
@@ -5681,7 +5681,7 @@
         <v>35240</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>232</v>
       </c>
@@ -5689,7 +5689,7 @@
         <v>259367959</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>73</v>
       </c>
@@ -5697,12 +5697,12 @@
         <v>63628</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>234</v>
       </c>
@@ -5711,7 +5711,7 @@
         <v>3716</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>235</v>
       </c>
@@ -5739,12 +5739,12 @@
     <col min="3" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>237</v>
       </c>
@@ -5767,12 +5767,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="40" t="s">
         <v>241</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="39">
         <f>$C$3-0.015</f>
         <v>0.12899451456771377</v>
@@ -5839,7 +5839,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="39">
         <f>$C$3-0.01</f>
         <v>0.13399451456771377</v>
@@ -5873,7 +5873,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="39">
         <f>$C$3-0.005</f>
         <v>0.13899451456771378</v>
@@ -5907,7 +5907,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="39">
         <f>$C$3</f>
         <v>0.14399451456771378</v>
@@ -5941,7 +5941,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="39">
         <f>$C$3+0.005</f>
         <v>0.14899451456771379</v>
@@ -5975,7 +5975,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="39">
         <f>$C$3+0.01</f>
         <v>0.15399451456771379</v>
@@ -6009,7 +6009,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="39">
         <f>$C$3+0.015</f>
         <v>0.1589945145677138</v>
@@ -6043,12 +6043,12 @@
         <v>537</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="40" t="s">
         <v>243</v>
       </c>
@@ -6081,7 +6081,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="39">
         <f>$C$3-0.015</f>
         <v>0.12899451456771377</v>
@@ -6115,7 +6115,7 @@
         <v>3208</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="39">
         <f>$C$3-0.01</f>
         <v>0.13399451456771377</v>
@@ -6149,7 +6149,7 @@
         <v>3136</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="39">
         <f>$C$3-0.005</f>
         <v>0.13899451456771378</v>
@@ -6183,7 +6183,7 @@
         <v>3065</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="39">
         <f>$C$3</f>
         <v>0.14399451456771378</v>
@@ -6217,7 +6217,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="39">
         <f>$C$3+0.005</f>
         <v>0.14899451456771379</v>
@@ -6251,7 +6251,7 @@
         <v>2929</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="39">
         <f>$C$3+0.01</f>
         <v>0.15399451456771379</v>
@@ -6285,7 +6285,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="39">
         <f>$C$3+0.015</f>
         <v>0.1589945145677138</v>
@@ -6319,7 +6319,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="45" t="s">
         <v>244</v>
       </c>
@@ -6356,12 +6356,12 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>246</v>
       </c>
@@ -6441,12 +6441,12 @@
         <v>266</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
         <v>268</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>270</v>
       </c>
@@ -6462,7 +6462,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>272</v>
       </c>
@@ -6470,7 +6470,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>274</v>
       </c>
@@ -6478,7 +6478,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>276</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>277</v>
       </c>
@@ -6494,7 +6494,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>279</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>281</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>283</v>
       </c>
@@ -6518,7 +6518,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>285</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>286</v>
       </c>
@@ -6534,7 +6534,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>287</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>288</v>
       </c>
@@ -6550,7 +6550,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>290</v>
       </c>
@@ -6558,7 +6558,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>291</v>
       </c>
@@ -6566,7 +6566,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>292</v>
       </c>
@@ -6574,7 +6574,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="29" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
         <v>294</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>296</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>298</v>
       </c>
@@ -6598,7 +6598,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="32" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>299</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>300</v>
       </c>
@@ -6614,7 +6614,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="34" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>301</v>
       </c>
@@ -6622,7 +6622,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="35" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>303</v>
       </c>
@@ -6630,7 +6630,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>305</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="37" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>307</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="38" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>309</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="39" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>311</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="40" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>313</v>
       </c>
@@ -6670,7 +6670,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="41" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>315</v>
       </c>
@@ -6678,7 +6678,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="42" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>317</v>
       </c>
@@ -6686,7 +6686,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>319</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="44" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>321</v>
       </c>
@@ -6702,7 +6702,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="45" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>322</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="46" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>324</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="47" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
         <v>326</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="48" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>328</v>
       </c>
@@ -6734,7 +6734,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="49" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>330</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="50" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>332</v>
       </c>
@@ -6750,7 +6750,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="51" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>334</v>
       </c>
@@ -6758,7 +6758,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="52" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>336</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="53" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>338</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="54" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>339</v>
       </c>
@@ -6782,7 +6782,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="55" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>341</v>
       </c>
@@ -6790,7 +6790,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="56" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
         <v>343</v>
       </c>
@@ -6798,7 +6798,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="57" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="4" t="s">
         <v>345</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="58" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
         <v>347</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="59" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
         <v>348</v>
       </c>
@@ -6822,7 +6822,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="60" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>350</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="61" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>352</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="62" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>354</v>
       </c>
@@ -6846,7 +6846,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="63" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>356</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="64" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
         <v>358</v>
       </c>
